--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,6 +877,123 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>115054680</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fiskvik, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>415051</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6570298</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Nordström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Nordström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -994,6 +994,125 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128248145</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92636</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gles tallskog, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>415204</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6570322</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erik Kihlsten</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erik Kihlsten</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128248145</v>
       </c>
       <c r="B5" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128248145</v>
       </c>
       <c r="B5" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Kihlsten</t>
+          <t>Erik Kihlsten, Åsa Duell</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128248145</v>
       </c>
       <c r="B5" t="n">
-        <v>92736</v>
+        <v>92742</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128248145</v>
       </c>
       <c r="B5" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128248145</v>
       </c>
       <c r="B5" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128248145</v>
       </c>
       <c r="B5" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128248145</v>
       </c>
       <c r="B5" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,7 +999,7 @@
         <v>128248145</v>
       </c>
       <c r="B5" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,6 +1112,124 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128887817</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92825</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Västra Löten, Västra Löten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>415150</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6570285</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128248145</v>
       </c>
       <c r="B5" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128887817</v>
       </c>
       <c r="B6" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128248145</v>
       </c>
       <c r="B5" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128887817</v>
       </c>
       <c r="B6" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128248145</v>
       </c>
       <c r="B5" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128887817</v>
       </c>
       <c r="B6" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128248145</v>
       </c>
       <c r="B5" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>128887817</v>
       </c>
       <c r="B6" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128248145</v>
       </c>
       <c r="B5" t="n">
-        <v>92805</v>
+        <v>92813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128887817</v>
       </c>
       <c r="B6" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>128887817</v>
       </c>
       <c r="B6" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>128887817</v>
       </c>
       <c r="B6" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>128887817</v>
       </c>
       <c r="B6" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>128887817</v>
       </c>
       <c r="B6" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>128887817</v>
       </c>
       <c r="B6" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>128887817</v>
       </c>
       <c r="B6" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112965638</v>
       </c>
       <c r="B2" t="n">
-        <v>90245</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,7 +710,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>415039</v>
+        <v>415038</v>
       </c>
       <c r="R2" t="n">
         <v>6570307</v>
@@ -777,50 +772,56 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112965636</v>
+        <v>128248145</v>
       </c>
       <c r="B3" t="n">
-        <v>89441</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5685</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västra Löten, Vrm</t>
+          <t>Gles tallskog, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>415035</v>
+        <v>415204</v>
       </c>
       <c r="R3" t="n">
-        <v>6570389</v>
+        <v>6570322</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -847,12 +848,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,75 +872,67 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Erik Kihlsten</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Erik Kihlsten, Åsa Duell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115054680</v>
+        <v>112965636</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5685</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fiskvik, Vrm</t>
+          <t>Västra Löten, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>415051</v>
+        <v>415036</v>
       </c>
       <c r="R4" t="n">
-        <v>6570298</v>
+        <v>6570389</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -953,22 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,29 +970,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Nordström</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Nordström</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128248145</v>
+        <v>112965639</v>
       </c>
       <c r="B5" t="n">
-        <v>92813</v>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,45 +999,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gles tallskog, Vrm</t>
+          <t>Västra Löten, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>415204</v>
+        <v>414965</v>
       </c>
       <c r="R5" t="n">
-        <v>6570322</v>
+        <v>6570313</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1072,22 +1053,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,19 +1067,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Kihlsten</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Kihlsten, Åsa Duell</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1118,7 +1088,7 @@
         <v>128887817</v>
       </c>
       <c r="B6" t="n">
-        <v>92863</v>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,6 +1200,331 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112965637</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Västra Löten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>415009</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6570296</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-10-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-10-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>115054680</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fiskvik, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>415051</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6570298</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Nordström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Nordström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124607659</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Parkeringen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>415114</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6570390</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alice Högström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alice Högström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61380-2023 artfynd.xlsx
+++ b/artfynd/A 61380-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112965638</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128248145</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112965636</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112965639</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887817</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,6 +1327,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112965637</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115054680</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1525,8 +1565,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124607659</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>